--- a/PPREstimation/output/top10/35_412_Gulf_of_Thailande_(1963).xlsx
+++ b/PPREstimation/output/top10/35_412_Gulf_of_Thailande_(1963).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -701,7 +700,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: nonliving detritus compartment; no species membership.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +788,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: primary producer group; species not listed.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -869,7 +876,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Zooplankton pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>2.052631578947368</v>
       </c>
@@ -953,7 +964,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Molluscs pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>2.210526315789473</v>
       </c>
@@ -1037,7 +1052,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Shrimps pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>2.417174515235457</v>
       </c>
@@ -1121,7 +1140,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Benthos pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>2.559556786703601</v>
       </c>
@@ -1205,7 +1228,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: trash fish; JSON abbreviated residual group. Its diet is 25% each phytoplankton, detritus, zooplankton and benthos. Species composition is not documented.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>2.653047091412742</v>
       </c>
@@ -1289,7 +1316,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Crab, lobster pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>2.7797783933518</v>
       </c>
@@ -1373,7 +1404,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Leiognathus. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>2.783656509695291</v>
       </c>
@@ -1457,7 +1492,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: sardine, anchovy. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>2.947368421052631</v>
       </c>
@@ -1541,7 +1580,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Rastrelliger. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>2.947368421052631</v>
       </c>
@@ -1625,7 +1668,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: generic jellyfish, included to represent presence; local species not listed.</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>3.052631578947368</v>
       </c>
@@ -1709,7 +1756,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Nemipterus, Pentaprion. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.186592797783933</v>
       </c>
@@ -1793,7 +1844,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Bothidae, Cynoglossidae. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.354459833795014</v>
       </c>
@@ -1877,7 +1932,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Rays pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>3.389362880886426</v>
       </c>
@@ -1961,7 +2020,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Plectorhynchus, Scolopsis, Upeneus, Pomadasys, Pampus, Arius, Tachysuridea. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>3.502054016620499</v>
       </c>
@@ -2045,7 +2108,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Priacanthus. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.344092797783933</v>
       </c>
@@ -2129,7 +2196,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: Cephalopods pool; individual species not listed.</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>3.381152128441404</v>
       </c>
@@ -2213,7 +2284,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Decapterus. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>3.527693905817174</v>
       </c>
@@ -2297,7 +2372,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Ephinephelus, Lutjanus. Juvenile grouper AND snapper compartment; JSON label is shortened. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>3.758987880886426</v>
       </c>
@@ -2381,7 +2460,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Trichiurus, Muraenesox, Chirocentrus, Sphyraena. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.736979916897508</v>
       </c>
@@ -2465,7 +2548,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: juvenile sharks; species and age/length threshold not listed.</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.736979916897507</v>
       </c>
@@ -2549,7 +2636,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Scomberomorus. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>3.909854005314036</v>
       </c>
@@ -2633,7 +2724,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Saurida, Lactarius, Lethrinus, Sciaenidae, Psettodes. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.379868264175476</v>
       </c>
@@ -2717,7 +2812,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Thunnus tonggol, Euthynnus affinis, Auxis thazard. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>4.134965175674147</v>
       </c>
@@ -2801,7 +2900,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Ephinephelus, Lutjanus. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>3.907286742396404</v>
       </c>
@@ -2885,7 +2988,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Christensen 1998 p.130 important components: Trichiurus, Muraenesox, Chirocentrus, Sphyraena. This is an illustrative list, not an exhaustive species inventory.</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>3.849934064178303</v>
       </c>
@@ -2969,7 +3076,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: adult sharks with a separate juvenile compartment; species not listed.</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>4.393943445131862</v>
       </c>
@@ -3053,7 +3164,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Christensen 1998 pp.130-131: generic marine mammals, parameterized from other ecosystems; local species not listed.</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>4.883427172745773</v>
       </c>
@@ -3277,9 +3392,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -3307,12 +3419,6 @@
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
@@ -3329,9 +3435,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3359,12 +3462,6 @@
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3478,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -3411,12 +3505,6 @@
       <c r="N4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" s="2" t="n">
         <v>1</v>
       </c>
@@ -3433,9 +3521,6 @@
           <t>Zooplankton</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>3.766889448417647</v>
       </c>
@@ -3463,17 +3548,11 @@
       <c r="N5" s="2" t="n">
         <v>4.03960396039604</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" s="2" t="n">
-        <v>5.401511704825688</v>
+        <v>5.425240142444302</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7.833845187536386</v>
+        <v>7.743871789112274</v>
       </c>
     </row>
     <row r="6">
@@ -3485,9 +3564,6 @@
           <t>Molluscs</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>6.884003273004893</v>
       </c>
@@ -3515,17 +3591,11 @@
       <c r="N6" s="2" t="n">
         <v>5.145346534653465</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" s="2" t="n">
-        <v>7.563154294965567</v>
+        <v>7.580280986574516</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>10.61557870560265</v>
+        <v>10.586653239631</v>
       </c>
     </row>
     <row r="7">
@@ -3537,9 +3607,6 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>9.725250712824778</v>
       </c>
@@ -3567,17 +3634,11 @@
       <c r="N7" s="2" t="n">
         <v>6.347110231023103</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" s="2" t="n">
-        <v>13.40018656776475</v>
+        <v>13.24153712362502</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>120.2574530317025</v>
+        <v>117.0055307006431</v>
       </c>
     </row>
     <row r="8">
@@ -3589,9 +3650,6 @@
           <t>Benthos</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>9.089087412848642</v>
       </c>
@@ -3619,17 +3677,11 @@
       <c r="N8" s="2" t="n">
         <v>7.897557755775578</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" s="2" t="n">
-        <v>13.7716793681741</v>
+        <v>13.71812954333685</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>135.4253360466695</v>
+        <v>133.1081593104837</v>
       </c>
     </row>
     <row r="9">
@@ -3641,9 +3693,6 @@
           <t>O.fish</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>15.35115677535972</v>
       </c>
@@ -3671,17 +3720,11 @@
       <c r="N9" s="2" t="n">
         <v>10.3497293729373</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" s="2" t="n">
-        <v>20.7320693422444</v>
+        <v>20.25999706454833</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>144.3177777679953</v>
+        <v>144.3046719082089</v>
       </c>
     </row>
     <row r="10">
@@ -3693,9 +3736,6 @@
           <t>Crab, lobster</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>20.13975733600306</v>
       </c>
@@ -3723,17 +3763,11 @@
       <c r="N10" s="2" t="n">
         <v>12.63609240924093</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" s="2" t="n">
-        <v>27.26644613560837</v>
+        <v>27.42290474872807</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>314.7811729012674</v>
+        <v>312.087764469793</v>
       </c>
     </row>
     <row r="11">
@@ -3745,9 +3779,6 @@
           <t>Ponyfishes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>18.86455159495139</v>
       </c>
@@ -3775,17 +3806,11 @@
       <c r="N11" s="2" t="n">
         <v>12.73967524752475</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" s="2" t="n">
-        <v>25.15088789704317</v>
+        <v>24.8754775610252</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>179.9421205478204</v>
+        <v>177.5798629411076</v>
       </c>
     </row>
     <row r="12">
@@ -3797,9 +3822,6 @@
           <t>Sm. pelagics</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>15.4672934703317</v>
       </c>
@@ -3827,17 +3849,11 @@
       <c r="N12" s="2" t="n">
         <v>11.9540594059406</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" s="2" t="n">
-        <v>20.19406563315881</v>
+        <v>20.40013583974687</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>30.1733124219317</v>
+        <v>29.97109110832151</v>
       </c>
     </row>
     <row r="13">
@@ -3849,9 +3865,6 @@
           <t>Mackerel</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>15.4672934703317</v>
       </c>
@@ -3879,17 +3892,11 @@
       <c r="N13" s="2" t="n">
         <v>11.9540594059406</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" s="2" t="n">
-        <v>19.89603122879168</v>
+        <v>20.38503937178309</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>29.69629807834289</v>
+        <v>29.83243457411026</v>
       </c>
     </row>
     <row r="14">
@@ -3901,9 +3908,6 @@
           <t>Jellyfish</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
         <v>16.69347778423553</v>
       </c>
@@ -3913,7 +3917,6 @@
       <c r="H14" s="2" t="n">
         <v>5.238879015485202</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" s="2" t="n">
         <v>0</v>
       </c>
@@ -3929,14 +3932,8 @@
       <c r="N14" s="2" t="n">
         <v>12.92673267326733</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" s="2" t="n">
-        <v>21.883710282263</v>
+        <v>21.77080708536177</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
@@ -3951,9 +3948,6 @@
           <t>Sm.dem.benth.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
         <v>27.099072781715</v>
       </c>
@@ -3981,17 +3975,11 @@
       <c r="N15" s="2" t="n">
         <v>17.31064227062706</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" s="2" t="n">
-        <v>36.46262646234926</v>
+        <v>36.03076554125405</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>335.3707779010479</v>
+        <v>325.8338644703285</v>
       </c>
     </row>
     <row r="16">
@@ -4003,9 +3991,6 @@
           <t>Flatfish</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
         <v>35.55627480985258</v>
       </c>
@@ -4033,17 +4018,11 @@
       <c r="N16" s="2" t="n">
         <v>21.36811553795379</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" s="2" t="n">
-        <v>47.51006777988365</v>
+        <v>47.53899942804074</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>460.2086472897706</v>
+        <v>442.7337249011892</v>
       </c>
     </row>
     <row r="17">
@@ -4055,9 +4034,6 @@
           <t>Rays</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>36.53348753682323</v>
       </c>
@@ -4085,17 +4061,11 @@
       <c r="N17" s="2" t="n">
         <v>27.81102639465514</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" s="2" t="n">
-        <v>62.76882853182445</v>
+        <v>63.1450496294759</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>649.8479606237934</v>
+        <v>630.5546089606922</v>
       </c>
     </row>
     <row r="18">
@@ -4107,9 +4077,6 @@
           <t>Med.dem.benth.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
         <v>40.46769255673753</v>
       </c>
@@ -4137,17 +4104,11 @@
       <c r="N18" s="2" t="n">
         <v>30.2691180990099</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" s="2" t="n">
-        <v>66.99674004007875</v>
+        <v>67.52559233847697</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>724.0518442790103</v>
+        <v>706.2547673627215</v>
       </c>
     </row>
     <row r="19">
@@ -4159,9 +4120,6 @@
           <t>Sm.dem.pisc.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
         <v>34.2577349342162</v>
       </c>
@@ -4189,17 +4147,11 @@
       <c r="N19" s="2" t="n">
         <v>19.85519440264027</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" s="2" t="n">
-        <v>44.35927536371812</v>
+        <v>44.41050953824529</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>351.3448930636328</v>
+        <v>355.5058722805248</v>
       </c>
     </row>
     <row r="20">
@@ -4211,9 +4163,6 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
         <v>35.26542502031035</v>
       </c>
@@ -4241,17 +4190,11 @@
       <c r="N20" s="2" t="n">
         <v>27.45885056679581</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" s="2" t="n">
-        <v>62.223399055655</v>
+        <v>61.37126990450257</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>373.0732570393848</v>
+        <v>358.7355862976431</v>
       </c>
     </row>
     <row r="21">
@@ -4263,9 +4206,6 @@
           <t>Scad</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
         <v>45.00023784560027</v>
       </c>
@@ -4293,17 +4233,11 @@
       <c r="N21" s="2" t="n">
         <v>26.03980293069307</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" s="2" t="n">
-        <v>55.75330712256239</v>
+        <v>55.58159910574945</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>202.2886029703636</v>
+        <v>196.8074356824083</v>
       </c>
     </row>
     <row r="22">
@@ -4315,9 +4249,6 @@
           <t>Juv. groupers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
         <v>78.40526108539161</v>
       </c>
@@ -4345,17 +4276,11 @@
       <c r="N22" s="2" t="n">
         <v>38.53443720871287</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" s="2" t="n">
-        <v>92.73234901758801</v>
+        <v>92.9951127626106</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>469.1762294592268</v>
+        <v>452.7453407020019</v>
       </c>
     </row>
     <row r="23">
@@ -4367,9 +4292,6 @@
           <t>Juv.Lg.Pisciv.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
         <v>66.07774080947139</v>
       </c>
@@ -4397,17 +4319,11 @@
       <c r="N23" s="2" t="n">
         <v>35.16255079920793</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" s="2" t="n">
-        <v>77.6585292700636</v>
+        <v>78.09506738106593</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>204.5398928716316</v>
+        <v>206.1215015021887</v>
       </c>
     </row>
     <row r="24">
@@ -4419,9 +4335,6 @@
           <t>Juv. sharks</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>66.07774080947139</v>
       </c>
@@ -4449,17 +4362,11 @@
       <c r="N24" s="2" t="n">
         <v>35.16255079920793</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" s="2" t="n">
-        <v>77.78414210701195</v>
+        <v>78.67717078237114</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>208.0090035529675</v>
+        <v>199.6757442946441</v>
       </c>
     </row>
     <row r="25">
@@ -4471,9 +4378,6 @@
           <t>Scomberomorus</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>91.36308066182804</v>
       </c>
@@ -4501,17 +4405,11 @@
       <c r="N25" s="2" t="n">
         <v>56.26565431137897</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" s="2" t="n">
-        <v>136.7424416504803</v>
+        <v>138.4083019678249</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>543.4948805698747</v>
+        <v>535.4806458943211</v>
       </c>
     </row>
     <row r="26">
@@ -4523,9 +4421,6 @@
           <t>Med.dem.pisc.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>40.28350859447509</v>
       </c>
@@ -4553,17 +4448,11 @@
       <c r="N26" s="2" t="n">
         <v>28.35152009973311</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" s="2" t="n">
-        <v>65.43541048894991</v>
+        <v>65.50305488453198</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>488.2030683636353</v>
+        <v>471.5357091260722</v>
       </c>
     </row>
     <row r="27">
@@ -4575,9 +4464,6 @@
           <t>Tuna</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
         <v>131.1605673316967</v>
       </c>
@@ -4605,17 +4491,11 @@
       <c r="N27" s="2" t="n">
         <v>73.82745225767599</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" s="2" t="n">
-        <v>185.2468118253964</v>
+        <v>192.014277521177</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>705.231622391423</v>
+        <v>708.3830194706286</v>
       </c>
     </row>
     <row r="28">
@@ -4627,9 +4507,6 @@
           <t>Grouper/snapper</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
         <v>102.9260652784837</v>
       </c>
@@ -4657,17 +4534,11 @@
       <c r="N28" s="2" t="n">
         <v>62.82297863772293</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" s="2" t="n">
-        <v>169.3163394434284</v>
+        <v>168.9250667696242</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1421.619291650378</v>
+        <v>1398.864017539258</v>
       </c>
     </row>
     <row r="29">
@@ -4679,9 +4550,6 @@
           <t>Lg. piscivores</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
         <v>90.59820923871769</v>
       </c>
@@ -4709,17 +4577,11 @@
       <c r="N29" s="2" t="n">
         <v>56.19877952093674</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" s="2" t="n">
-        <v>138.9897785373972</v>
+        <v>141.0827965751483</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>884.9362957238095</v>
+        <v>853.5305577109121</v>
       </c>
     </row>
     <row r="30">
@@ -4731,9 +4593,6 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
         <v>239.2609978080322</v>
       </c>
@@ -4761,17 +4620,11 @@
       <c r="N30" s="2" t="n">
         <v>131.1717908978514</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" s="2" t="n">
-        <v>389.3220252720494</v>
+        <v>405.5567610058406</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>2193.192955651655</v>
+        <v>2124.182848338417</v>
       </c>
     </row>
     <row r="31">
@@ -4783,9 +4636,6 @@
           <t>M. mammals</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
         <v>414.206748009181</v>
       </c>
@@ -4795,7 +4645,6 @@
       <c r="H31" s="2" t="n">
         <v>198.3875688998984</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>0</v>
       </c>
@@ -4811,14 +4660,8 @@
       <c r="N31" s="2" t="n">
         <v>26057.36883611624</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" s="2" t="n">
-        <v>80914.23676913242</v>
+        <v>81709.98799357255</v>
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
@@ -5019,12 +4862,6 @@
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
@@ -5077,17 +4914,11 @@
       <c r="N3" s="2" t="n">
         <v>2.88398472576648</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" s="2" t="n">
-        <v>2.636632674770888</v>
+        <v>2.629562646323063</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6921421872535002</v>
+        <v>0.6891383286453481</v>
       </c>
     </row>
     <row r="4">
@@ -5135,12 +4966,6 @@
       <c r="N4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" s="2" t="n">
         <v>1</v>
       </c>
@@ -5193,17 +5018,11 @@
       <c r="N5" s="2" t="n">
         <v>5.410210562740506</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" s="2" t="n">
-        <v>7.104416513538675</v>
+        <v>7.131021502104752</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>8.476732093869396</v>
+        <v>8.377866016624989</v>
       </c>
     </row>
     <row r="6">
@@ -5251,17 +5070,11 @@
       <c r="N6" s="2" t="n">
         <v>6.022534760153924</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" s="2" t="n">
-        <v>8.928714117509664</v>
+        <v>8.947789859642743</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>11.19281717836193</v>
+        <v>11.15628899878889</v>
       </c>
     </row>
     <row r="7">
@@ -5309,17 +5122,11 @@
       <c r="N7" s="2" t="n">
         <v>16.79886015144591</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" s="2" t="n">
-        <v>27.98915968088473</v>
+        <v>27.61086673064081</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>137.9494986508325</v>
+        <v>134.2340825475453</v>
       </c>
     </row>
     <row r="8">
@@ -5367,17 +5174,11 @@
       <c r="N8" s="2" t="n">
         <v>13.44916716508131</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" s="2" t="n">
-        <v>21.64107889411871</v>
+        <v>21.49091370816712</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>153.1585811681476</v>
+        <v>150.5385962411484</v>
       </c>
     </row>
     <row r="9">
@@ -5425,17 +5226,11 @@
       <c r="N9" s="2" t="n">
         <v>18.19468996287063</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" s="2" t="n">
-        <v>33.30800739206767</v>
+        <v>32.42947243067172</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>163.4303495384066</v>
+        <v>163.4108729841161</v>
       </c>
     </row>
     <row r="10">
@@ -5483,17 +5278,11 @@
       <c r="N10" s="2" t="n">
         <v>26.13304302535646</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" s="2" t="n">
-        <v>48.06145932045817</v>
+        <v>48.21597172946623</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>357.5117767736681</v>
+        <v>354.4675887538862</v>
       </c>
     </row>
     <row r="11">
@@ -5541,17 +5330,11 @@
       <c r="N11" s="2" t="n">
         <v>19.38500261870894</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" s="2" t="n">
-        <v>36.88760807677443</v>
+        <v>36.37255908308947</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>202.7895547719528</v>
+        <v>200.1370740273283</v>
       </c>
     </row>
     <row r="12">
@@ -5599,17 +5382,11 @@
       <c r="N12" s="2" t="n">
         <v>15.90140642069266</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" s="2" t="n">
-        <v>26.43561480559173</v>
+        <v>26.70135798770155</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>32.61746764757513</v>
+        <v>32.39206479916432</v>
       </c>
     </row>
     <row r="13">
@@ -5657,17 +5434,11 @@
       <c r="N13" s="2" t="n">
         <v>15.90140642069266</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" s="2" t="n">
-        <v>26.03533492594572</v>
+        <v>26.67937939595116</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>32.10186970242317</v>
+        <v>32.24210052753474</v>
       </c>
     </row>
     <row r="14">
@@ -5697,7 +5468,6 @@
       <c r="H14" s="2" t="n">
         <v>5.855217723189344</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" s="2" t="n">
         <v>0</v>
       </c>
@@ -5713,14 +5483,8 @@
       <c r="N14" s="2" t="n">
         <v>17.31267380076962</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" s="2" t="n">
-        <v>28.7877552101274</v>
+        <v>28.63326426871092</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
@@ -5771,17 +5535,11 @@
       <c r="N15" s="2" t="n">
         <v>30.43851385231989</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" s="2" t="n">
-        <v>58.92892176369728</v>
+        <v>58.08791606427388</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>379.8144619375678</v>
+        <v>369.1094243865741</v>
       </c>
     </row>
     <row r="16">
@@ -5829,17 +5587,11 @@
       <c r="N16" s="2" t="n">
         <v>38.35185593373934</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" s="2" t="n">
-        <v>77.34324987430435</v>
+        <v>77.14257598014585</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>521.3107204488086</v>
+        <v>501.5558102103201</v>
       </c>
     </row>
     <row r="17">
@@ -5887,17 +5639,11 @@
       <c r="N17" s="2" t="n">
         <v>50.91046827295949</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" s="2" t="n">
-        <v>103.4928677105613</v>
+        <v>103.8104625686485</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>736.4914866620303</v>
+        <v>714.5229959820447</v>
       </c>
     </row>
     <row r="18">
@@ -5945,17 +5691,11 @@
       <c r="N18" s="2" t="n">
         <v>53.74061414320809</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" s="2" t="n">
-        <v>108.4397519452302</v>
+        <v>108.8698337281783</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>820.0063533827949</v>
+        <v>799.6778774752461</v>
       </c>
     </row>
     <row r="19">
@@ -6003,17 +5743,11 @@
       <c r="N19" s="2" t="n">
         <v>38.00869244819479</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" s="2" t="n">
-        <v>76.22362812766491</v>
+        <v>76.06303147811174</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>399.2872591826044</v>
+        <v>403.9677184100817</v>
       </c>
     </row>
     <row r="20">
@@ -6061,17 +5795,11 @@
       <c r="N20" s="2" t="n">
         <v>49.64368086051377</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" s="2" t="n">
-        <v>102.6858247770239</v>
+        <v>100.9579937995787</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>423.3725011186399</v>
+        <v>407.0590343241895</v>
       </c>
     </row>
     <row r="21">
@@ -6119,17 +5847,11 @@
       <c r="N21" s="2" t="n">
         <v>39.00375518410398</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" s="2" t="n">
-        <v>79.92029395660073</v>
+        <v>79.58018547371164</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>226.5735214283972</v>
+        <v>220.3508395022479</v>
       </c>
     </row>
     <row r="22">
@@ -6177,17 +5899,11 @@
       <c r="N22" s="2" t="n">
         <v>58.01819019573802</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" s="2" t="n">
-        <v>133.8895485431987</v>
+        <v>133.8954930610666</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>526.4824677022142</v>
+        <v>507.8730374775016</v>
       </c>
     </row>
     <row r="23">
@@ -6235,17 +5951,11 @@
       <c r="N23" s="2" t="n">
         <v>48.20570412687407</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" s="2" t="n">
-        <v>104.4319618853663</v>
+        <v>104.9802717580872</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>225.136073537808</v>
+        <v>226.7381624294625</v>
       </c>
     </row>
     <row r="24">
@@ -6293,17 +6003,11 @@
       <c r="N24" s="2" t="n">
         <v>48.20570412687407</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" s="2" t="n">
-        <v>104.6347803360973</v>
+        <v>105.7591966234671</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>228.9141185374869</v>
+        <v>219.6002639928552</v>
       </c>
     </row>
     <row r="25">
@@ -6351,17 +6055,11 @@
       <c r="N25" s="2" t="n">
         <v>85.80764504531936</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" s="2" t="n">
-        <v>199.3640653322248</v>
+        <v>201.3939657633522</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>610.0711119548997</v>
+        <v>601.0195585056825</v>
       </c>
     </row>
     <row r="26">
@@ -6409,17 +6107,11 @@
       <c r="N26" s="2" t="n">
         <v>51.59243915254069</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" s="2" t="n">
-        <v>108.7471131485804</v>
+        <v>108.4873871930121</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>553.8409781537688</v>
+        <v>535.0091730086642</v>
       </c>
     </row>
     <row r="27">
@@ -6467,17 +6159,11 @@
       <c r="N27" s="2" t="n">
         <v>107.8626925263291</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" s="2" t="n">
-        <v>261.8364564206431</v>
+        <v>271.5037037411298</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>788.1384587709446</v>
+        <v>791.5983927627544</v>
       </c>
     </row>
     <row r="28">
@@ -6525,17 +6211,11 @@
       <c r="N28" s="2" t="n">
         <v>111.7423134607598</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" s="2" t="n">
-        <v>275.5399497040818</v>
+        <v>273.9089312070992</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1611.072375803513</v>
+        <v>1584.88760675104</v>
       </c>
     </row>
     <row r="29">
@@ -6583,17 +6263,11 @@
       <c r="N29" s="2" t="n">
         <v>89.62093563311703</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" s="2" t="n">
-        <v>211.2289131019431</v>
+        <v>213.6900113491415</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>998.3566475765674</v>
+        <v>962.9311990402859</v>
       </c>
     </row>
     <row r="30">
@@ -6641,17 +6315,11 @@
       <c r="N30" s="2" t="n">
         <v>207.9562738839305</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" s="2" t="n">
-        <v>584.4145240516937</v>
+        <v>606.9739063292308</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>2471.733238219147</v>
+        <v>2393.658992550364</v>
       </c>
     </row>
     <row r="31">
@@ -6681,7 +6349,6 @@
       <c r="H31" s="2" t="n">
         <v>233.1149286258984</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>0</v>
       </c>
@@ -6697,14 +6364,8 @@
       <c r="N31" s="2" t="n">
         <v>38861.87639095054</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" s="2" t="n">
-        <v>116107.6886651785</v>
+        <v>117114.6114691534</v>
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
@@ -6905,12 +6566,6 @@
       <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
@@ -6963,17 +6618,11 @@
       <c r="N3" s="2" t="n">
         <v>2.88398472576648</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" s="2" t="n">
-        <v>2.636632674770888</v>
+        <v>2.629562646323063</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6921421872535002</v>
+        <v>0.6891383286453481</v>
       </c>
     </row>
     <row r="4">
@@ -7021,12 +6670,6 @@
       <c r="N4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" s="2" t="n">
         <v>1</v>
       </c>
@@ -7079,17 +6722,11 @@
       <c r="N5" s="2" t="n">
         <v>5.410210562740506</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" s="2" t="n">
-        <v>7.104416513538675</v>
+        <v>7.131021502104752</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>8.476732093869396</v>
+        <v>8.377866016624989</v>
       </c>
     </row>
     <row r="6">
@@ -7137,17 +6774,11 @@
       <c r="N6" s="2" t="n">
         <v>6.022534760153924</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" s="2" t="n">
-        <v>8.928714117509664</v>
+        <v>8.947789859642743</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>11.19281717836193</v>
+        <v>11.15628899878889</v>
       </c>
     </row>
     <row r="7">
@@ -7195,17 +6826,11 @@
       <c r="N7" s="2" t="n">
         <v>16.79886015144591</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" s="2" t="n">
-        <v>27.98915968088473</v>
+        <v>27.61086673064081</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>137.9494986508325</v>
+        <v>134.2340825475453</v>
       </c>
     </row>
     <row r="8">
@@ -7253,17 +6878,11 @@
       <c r="N8" s="2" t="n">
         <v>13.44916716508131</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" s="2" t="n">
-        <v>21.64107889411871</v>
+        <v>21.49091370816712</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>153.1585811681476</v>
+        <v>150.5385962411484</v>
       </c>
     </row>
     <row r="9">
@@ -7311,17 +6930,11 @@
       <c r="N9" s="2" t="n">
         <v>18.19468996287063</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" s="2" t="n">
-        <v>33.30800739206767</v>
+        <v>32.42947243067172</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>163.4303495384066</v>
+        <v>163.4108729841161</v>
       </c>
     </row>
     <row r="10">
@@ -7369,17 +6982,11 @@
       <c r="N10" s="2" t="n">
         <v>26.13304302535646</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" s="2" t="n">
-        <v>48.06145932045817</v>
+        <v>48.21597172946623</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>357.5117767736681</v>
+        <v>354.4675887538862</v>
       </c>
     </row>
     <row r="11">
@@ -7427,17 +7034,11 @@
       <c r="N11" s="2" t="n">
         <v>19.38500261870894</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" s="2" t="n">
-        <v>36.88760807677443</v>
+        <v>36.37255908308947</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>202.7895547719528</v>
+        <v>200.1370740273283</v>
       </c>
     </row>
     <row r="12">
@@ -7485,17 +7086,11 @@
       <c r="N12" s="2" t="n">
         <v>15.90140642069266</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" s="2" t="n">
-        <v>26.43561480559173</v>
+        <v>26.70135798770155</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>32.61746764757513</v>
+        <v>32.39206479916432</v>
       </c>
     </row>
     <row r="13">
@@ -7543,17 +7138,11 @@
       <c r="N13" s="2" t="n">
         <v>15.90140642069266</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" s="2" t="n">
-        <v>26.03533492594572</v>
+        <v>26.67937939595116</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>32.10186970242317</v>
+        <v>32.24210052753474</v>
       </c>
     </row>
     <row r="14">
@@ -7601,14 +7190,8 @@
       <c r="N14" s="2" t="n">
         <v>17.31267380076962</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" s="2" t="n">
-        <v>28.7877552101274</v>
+        <v>28.63326426871092</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
@@ -7659,17 +7242,11 @@
       <c r="N15" s="2" t="n">
         <v>30.43851385231989</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" s="2" t="n">
-        <v>58.92892176369728</v>
+        <v>58.08791606427388</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>379.8144619375678</v>
+        <v>369.1094243865741</v>
       </c>
     </row>
     <row r="16">
@@ -7717,17 +7294,11 @@
       <c r="N16" s="2" t="n">
         <v>38.35185593373934</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" s="2" t="n">
-        <v>77.34324987430435</v>
+        <v>77.14257598014585</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>521.3107204488086</v>
+        <v>501.5558102103201</v>
       </c>
     </row>
     <row r="17">
@@ -7775,17 +7346,11 @@
       <c r="N17" s="2" t="n">
         <v>50.91046827295949</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" s="2" t="n">
-        <v>103.4928677105613</v>
+        <v>103.8104625686485</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>736.4914866620303</v>
+        <v>714.5229959820447</v>
       </c>
     </row>
     <row r="18">
@@ -7833,17 +7398,11 @@
       <c r="N18" s="2" t="n">
         <v>53.74061414320809</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" s="2" t="n">
-        <v>108.4397519452302</v>
+        <v>108.8698337281783</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>820.0063533827949</v>
+        <v>799.6778774752461</v>
       </c>
     </row>
     <row r="19">
@@ -7891,17 +7450,11 @@
       <c r="N19" s="2" t="n">
         <v>38.00869244819479</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" s="2" t="n">
-        <v>76.22362812766491</v>
+        <v>76.06303147811174</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>399.2872591826044</v>
+        <v>403.9677184100817</v>
       </c>
     </row>
     <row r="20">
@@ -7949,17 +7502,11 @@
       <c r="N20" s="2" t="n">
         <v>49.64368086051377</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" s="2" t="n">
-        <v>102.6858247770239</v>
+        <v>100.9579937995787</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>423.3725011186399</v>
+        <v>407.0590343241895</v>
       </c>
     </row>
     <row r="21">
@@ -8007,17 +7554,11 @@
       <c r="N21" s="2" t="n">
         <v>39.00375518410398</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" s="2" t="n">
-        <v>79.92029395660073</v>
+        <v>79.58018547371164</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>226.5735214283972</v>
+        <v>220.3508395022479</v>
       </c>
     </row>
     <row r="22">
@@ -8065,17 +7606,11 @@
       <c r="N22" s="2" t="n">
         <v>58.01819019573802</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" s="2" t="n">
-        <v>133.8895485431987</v>
+        <v>133.8954930610666</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>526.4824677022142</v>
+        <v>507.8730374775016</v>
       </c>
     </row>
     <row r="23">
@@ -8123,17 +7658,11 @@
       <c r="N23" s="2" t="n">
         <v>48.20570412687407</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" s="2" t="n">
-        <v>104.4319618853663</v>
+        <v>104.9802717580872</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>225.136073537808</v>
+        <v>226.7381624294625</v>
       </c>
     </row>
     <row r="24">
@@ -8181,17 +7710,11 @@
       <c r="N24" s="2" t="n">
         <v>48.20570412687407</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" s="2" t="n">
-        <v>104.6347803360973</v>
+        <v>105.7591966234671</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>228.9141185374869</v>
+        <v>219.6002639928552</v>
       </c>
     </row>
     <row r="25">
@@ -8239,17 +7762,11 @@
       <c r="N25" s="2" t="n">
         <v>85.80764504531936</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" s="2" t="n">
-        <v>199.3640653322248</v>
+        <v>201.3939657633522</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>610.0711119548997</v>
+        <v>601.0195585056825</v>
       </c>
     </row>
     <row r="26">
@@ -8297,17 +7814,11 @@
       <c r="N26" s="2" t="n">
         <v>51.59243915254069</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" s="2" t="n">
-        <v>108.7471131485804</v>
+        <v>108.4873871930121</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>553.8409781537688</v>
+        <v>535.0091730086642</v>
       </c>
     </row>
     <row r="27">
@@ -8355,17 +7866,11 @@
       <c r="N27" s="2" t="n">
         <v>107.8626925263291</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" s="2" t="n">
-        <v>261.8364564206431</v>
+        <v>271.5037037411298</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>788.1384587709446</v>
+        <v>791.5983927627544</v>
       </c>
     </row>
     <row r="28">
@@ -8413,17 +7918,11 @@
       <c r="N28" s="2" t="n">
         <v>111.7423134607598</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" s="2" t="n">
-        <v>275.5399497040818</v>
+        <v>273.9089312070992</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1611.072375803513</v>
+        <v>1584.88760675104</v>
       </c>
     </row>
     <row r="29">
@@ -8471,17 +7970,11 @@
       <c r="N29" s="2" t="n">
         <v>89.62093563311703</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" s="2" t="n">
-        <v>211.2289131019431</v>
+        <v>213.6900113491415</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>998.3566475765674</v>
+        <v>962.9311990402859</v>
       </c>
     </row>
     <row r="30">
@@ -8529,17 +8022,11 @@
       <c r="N30" s="2" t="n">
         <v>207.9562738839305</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" s="2" t="n">
-        <v>584.4145240516937</v>
+        <v>606.9739063292308</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>2471.733238219147</v>
+        <v>2393.658992550364</v>
       </c>
     </row>
     <row r="31">
@@ -8587,14 +8074,8 @@
       <c r="N31" s="2" t="n">
         <v>38861.87639095054</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" s="2" t="n">
-        <v>116107.6886651785</v>
+        <v>117114.6114691534</v>
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
@@ -9069,7 +8550,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.2712203663435123</v>
       </c>
@@ -9195,7 +8675,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Gulf_of_Thailande (1963)</t>
@@ -9259,7 +8738,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -9299,7 +8777,6 @@
       <c r="AP3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -9451,7 +8928,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.2984439309247964</v>
       </c>
@@ -9614,14 +9090,12 @@
       <c r="C2" s="2" t="n">
         <v>1081.93669776113</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.296421013085241</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9635,14 +9109,12 @@
       <c r="C3" s="2" t="n">
         <v>1825.633274645668</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.5001734999029226</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9656,14 +9128,12 @@
       <c r="C4" s="2" t="n">
         <v>272.6487018382484</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.07469827447623242</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9896,12 +9366,6 @@
           <t>sym_TE_asPP</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -9909,12 +9373,6 @@
           <t>sym_TE_asDC</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -9922,12 +9380,6 @@
           <t>sym_GE_asPP</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -9935,12 +9387,6 @@
           <t>sym_GE_asDC</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -9948,12 +9394,6 @@
           <t>sym_WithEgestion_asPP</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -9961,12 +9401,6 @@
           <t>sym_WithEgestion_asDC</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -9975,22 +9409,22 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>741.2698670375272</v>
+        <v>737.7642718622931</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>741.2698670375272</v>
+        <v>737.7642718622931</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>471.3708563504958</v>
+        <v>470.6597780235485</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.203087634804802</v>
+        <v>0.2021271977704913</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.1291427003699988</v>
+        <v>0.1289478843900133</v>
       </c>
     </row>
     <row r="21">
@@ -10000,22 +9434,22 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3332.772910373853</v>
+        <v>3262.663284487827</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3332.772910373853</v>
+        <v>3262.663284487827</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2946.614660463898</v>
+        <v>2884.868903916717</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.9130884685955762</v>
+        <v>0.8938803519144731</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8072916877983282</v>
+        <v>0.7903750421689635</v>
       </c>
     </row>
   </sheetData>
@@ -10091,10 +9525,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -10119,10 +9553,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -10187,7 +9621,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -10200,7 +9633,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -10213,7 +9645,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -10226,7 +9657,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -10239,7 +9669,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -10252,7 +9681,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -10265,7 +9693,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -10278,7 +9705,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -10291,7 +9717,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10318,7 +9743,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10335,7 +9760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/35_412_Gulf_of_Thailande_(1963).xlsx
+++ b/PPREstimation/output/top10/35_412_Gulf_of_Thailande_(1963).xlsx
@@ -3244,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3382,6 +3382,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3425,6 +3435,9 @@
       <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -3468,6 +3481,9 @@
       <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -3511,6 +3527,9 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -3522,7 +3541,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.766889448417647</v>
+        <v>5.540572006885044</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.238879015485202</v>
@@ -3553,6 +3572,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7.743871789112274</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.766889448417648</v>
       </c>
     </row>
     <row r="6">
@@ -3565,7 +3587,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.884003273004893</v>
+        <v>12.43770028023961</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8.212336902653513</v>
@@ -3596,6 +3618,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>10.586653239631</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6.884003273004896</v>
       </c>
     </row>
     <row r="7">
@@ -3608,7 +3633,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9.725250712824778</v>
+        <v>29.42849932184621</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30.20134835397714</v>
@@ -3639,6 +3664,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>117.0055307006431</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9.725250712824785</v>
       </c>
     </row>
     <row r="8">
@@ -3651,7 +3679,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>9.089087412848642</v>
+        <v>19.80339807871102</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>33.24466166260525</v>
@@ -3682,6 +3710,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>133.1081593104837</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.089087412848647</v>
       </c>
     </row>
     <row r="9">
@@ -3694,7 +3725,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>15.35115677535972</v>
+        <v>42.92960682543251</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>39.53676903023585</v>
@@ -3725,6 +3756,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>144.3046719082089</v>
+      </c>
+      <c r="X9" t="n">
+        <v>15.35115677535973</v>
       </c>
     </row>
     <row r="10">
@@ -3737,7 +3771,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>20.13975733600306</v>
+        <v>64.54244296241608</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>77.51268457771762</v>
@@ -3768,6 +3802,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>312.087764469793</v>
+      </c>
+      <c r="X10" t="n">
+        <v>20.13975733600308</v>
       </c>
     </row>
     <row r="11">
@@ -3780,7 +3817,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>18.86455159495139</v>
+        <v>52.16736019132902</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>49.1695491765569</v>
@@ -3811,6 +3848,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>177.5798629411076</v>
+      </c>
+      <c r="X11" t="n">
+        <v>18.8645515949514</v>
       </c>
     </row>
     <row r="12">
@@ -3823,7 +3863,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>15.4672934703317</v>
+        <v>33.15553123272806</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>20.27364679552287</v>
@@ -3854,6 +3894,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>29.97109110832151</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15.46729347033171</v>
       </c>
     </row>
     <row r="13">
@@ -3866,7 +3909,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>15.4672934703317</v>
+        <v>33.15553123272806</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>20.27364679552287</v>
@@ -3897,6 +3940,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>29.83243457411026</v>
+      </c>
+      <c r="X13" t="n">
+        <v>15.46729347033171</v>
       </c>
     </row>
     <row r="14">
@@ -3909,7 +3955,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>16.69347778423553</v>
+        <v>36.11522136879783</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -3937,6 +3983,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16.69347778423554</v>
       </c>
     </row>
     <row r="15">
@@ -3949,7 +3998,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>27.099072781715</v>
+        <v>85.26248051124689</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>87.40012975364368</v>
@@ -3980,6 +4029,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>325.8338644703285</v>
+      </c>
+      <c r="X15" t="n">
+        <v>27.09907278171502</v>
       </c>
     </row>
     <row r="16">
@@ -3992,7 +4044,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>35.55627480985258</v>
+        <v>117.6491488003211</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>112.6758719563085</v>
@@ -4023,6 +4075,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>442.7337249011892</v>
+      </c>
+      <c r="X16" t="n">
+        <v>35.55627480985261</v>
       </c>
     </row>
     <row r="17">
@@ -4035,7 +4090,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>36.53348753682323</v>
+        <v>122.4503463336606</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>155.4832650270813</v>
@@ -4066,6 +4121,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>630.5546089606922</v>
+      </c>
+      <c r="X17" t="n">
+        <v>36.53348753682326</v>
       </c>
     </row>
     <row r="18">
@@ -4078,7 +4136,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>40.46769255673753</v>
+        <v>136.9097994647181</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>177.0042115165573</v>
@@ -4109,6 +4167,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>706.2547673627215</v>
+      </c>
+      <c r="X18" t="n">
+        <v>40.46769255673757</v>
       </c>
     </row>
     <row r="19">
@@ -4121,7 +4182,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>34.2577349342162</v>
+        <v>122.9045517934178</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>93.21507153837017</v>
@@ -4152,6 +4213,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>355.5058722805248</v>
+      </c>
+      <c r="X19" t="n">
+        <v>34.25773493421622</v>
       </c>
     </row>
     <row r="20">
@@ -4164,7 +4228,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>35.26542502031035</v>
+        <v>123.705653792</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>98.83276256062474</v>
@@ -4195,6 +4259,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>358.7355862976431</v>
+      </c>
+      <c r="X20" t="n">
+        <v>35.26542502031037</v>
       </c>
     </row>
     <row r="21">
@@ -4207,7 +4274,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45.00023784560027</v>
+        <v>145.1700444662526</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>76.90318242862737</v>
@@ -4238,6 +4305,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>196.8074356824083</v>
+      </c>
+      <c r="X21" t="n">
+        <v>45.0002378456003</v>
       </c>
     </row>
     <row r="22">
@@ -4250,7 +4320,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>78.40526108539161</v>
+        <v>314.9491257892457</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>164.924276869733</v>
@@ -4281,6 +4351,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>452.7453407020019</v>
+      </c>
+      <c r="X22" t="n">
+        <v>78.40526108539169</v>
       </c>
     </row>
     <row r="23">
@@ -4293,7 +4366,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>66.07774080947139</v>
+        <v>235.1320645208407</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>107.1308501241101</v>
@@ -4324,6 +4397,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>206.1215015021887</v>
+      </c>
+      <c r="X23" t="n">
+        <v>66.07774080947146</v>
       </c>
     </row>
     <row r="24">
@@ -4336,7 +4412,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>66.07774080947139</v>
+        <v>235.1320645208407</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>107.1308501241101</v>
@@ -4367,6 +4443,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>199.6757442946441</v>
+      </c>
+      <c r="X24" t="n">
+        <v>66.07774080947146</v>
       </c>
     </row>
     <row r="25">
@@ -4379,7 +4458,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>91.36308066182804</v>
+        <v>379.2120036036188</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>198.0073097218141</v>
@@ -4410,6 +4489,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>535.4806458943211</v>
+      </c>
+      <c r="X25" t="n">
+        <v>91.36308066182814</v>
       </c>
     </row>
     <row r="26">
@@ -4422,7 +4504,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>40.28350859447509</v>
+        <v>155.3356600809242</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>128.3791845779764</v>
@@ -4453,6 +4535,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>471.5357091260722</v>
+      </c>
+      <c r="X26" t="n">
+        <v>40.28350859447513</v>
       </c>
     </row>
     <row r="27">
@@ -4465,7 +4550,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>131.1605673316967</v>
+        <v>607.7580800975992</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>280.5750088183167</v>
@@ -4496,6 +4581,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>708.3830194706286</v>
+      </c>
+      <c r="X27" t="n">
+        <v>131.1605673316968</v>
       </c>
     </row>
     <row r="28">
@@ -4508,7 +4596,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>102.9260652784837</v>
+        <v>490.511950708471</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>374.2982340071972</v>
@@ -4539,6 +4627,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>1398.864017539258</v>
+      </c>
+      <c r="X28" t="n">
+        <v>102.9260652784838</v>
       </c>
     </row>
     <row r="29">
@@ -4551,7 +4642,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>90.59820923871769</v>
+        <v>401.2339602182657</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>262.0575925413299</v>
@@ -4582,6 +4673,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>853.5305577109121</v>
+      </c>
+      <c r="X29" t="n">
+        <v>90.59820923871777</v>
       </c>
     </row>
     <row r="30">
@@ -4594,7 +4688,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>239.2609978080322</v>
+        <v>1428.928099091568</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>692.9071953512632</v>
@@ -4626,6 +4720,9 @@
       <c r="V30" s="2" t="n">
         <v>2124.182848338417</v>
       </c>
+      <c r="X30" t="n">
+        <v>239.2609978080325</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -4637,7 +4734,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>414.206748009181</v>
+        <v>2621.612931714263</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -4665,6 +4762,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>414.2067480091815</v>
       </c>
     </row>
   </sheetData>
@@ -4678,7 +4778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4816,6 +4916,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4868,6 +4978,12 @@
       <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -4920,6 +5036,12 @@
       <c r="V3" s="2" t="n">
         <v>0.6891383286453481</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -4972,6 +5094,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -4989,10 +5117,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.431634645197231</v>
+        <v>6.518320008100051</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.21005291293737</v>
+        <v>6.192404007695049</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.855217723189344</v>
@@ -5023,6 +5151,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>8.377866016624989</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.431634645197233</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.210052912937371</v>
       </c>
     </row>
     <row r="6">
@@ -5041,10 +5175,10 @@
         <v>15.84893192461114</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.968658602597495</v>
+        <v>9.483372579397724</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.276790985575142</v>
+        <v>13.28747019479956</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8.760193531723861</v>
@@ -5075,6 +5209,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>11.15628899878889</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.968658602597497</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7.276790985575144</v>
       </c>
     </row>
     <row r="7">
@@ -5093,10 +5233,10 @@
         <v>24.93687941796677</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8.001064059813308</v>
+        <v>13.71573211049736</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14.97556970612542</v>
+        <v>39.54220137686472</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>39.34555692831442</v>
@@ -5127,6 +5267,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>134.2340825475453</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.001064059813311</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14.97556970612543</v>
       </c>
     </row>
     <row r="8">
@@ -5145,10 +5291,10 @@
         <v>30.49372829387258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.112489038063083</v>
+        <v>16.15655423361635</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11.29118781331001</v>
+        <v>23.73538752207881</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40.2952399907787</v>
@@ -5179,6 +5325,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>150.5385962411484</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9.112489038063087</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.29118781331002</v>
       </c>
     </row>
     <row r="9">
@@ -5197,10 +5349,10 @@
         <v>41.78810060294223</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.17156947859833</v>
+        <v>20.88126393867481</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>19.38977618409366</v>
+        <v>52.02889058574307</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>48.21537006668882</v>
@@ -5231,6 +5383,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>163.4108729841161</v>
+      </c>
+      <c r="W9" t="n">
+        <v>11.17156947859834</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.38977618409368</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5407,10 @@
         <v>55.22112665807593</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.37773098302224</v>
+        <v>26.20052834456147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27.23502687204532</v>
+        <v>80.61658569663733</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>96.28327532558015</v>
@@ -5283,6 +5441,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>354.4675887538862</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13.37773098302224</v>
+      </c>
+      <c r="X10" t="n">
+        <v>27.23502687204535</v>
       </c>
     </row>
     <row r="11">
@@ -5301,10 +5465,10 @@
         <v>55.6241205887029</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.44077277831944</v>
+        <v>26.35609133602047</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>22.38140449187295</v>
+        <v>61.13100470127168</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>58.6373656133773</v>
@@ -5335,6 +5499,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>200.1370740273283</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13.44077277831945</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22.38140449187296</v>
       </c>
     </row>
     <row r="12">
@@ -5353,10 +5523,10 @@
         <v>79.43282347242813</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.92277198657578</v>
+        <v>35.22555040278327</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17.23483817689782</v>
+        <v>36.97949584824783</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>22.60924610892804</v>
@@ -5387,6 +5557,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>32.39206479916432</v>
+      </c>
+      <c r="W12" t="n">
+        <v>16.9227719865758</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.23483817689783</v>
       </c>
     </row>
     <row r="13">
@@ -5405,10 +5581,10 @@
         <v>79.43282347242813</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16.92277198657578</v>
+        <v>35.22555040278324</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>17.23483817689782</v>
+        <v>36.97949584824783</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>22.60924610892804</v>
@@ -5439,6 +5615,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>32.24210052753474</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.92277198657579</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.23483817689783</v>
       </c>
     </row>
     <row r="14">
@@ -5457,10 +5639,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.6393856285124</v>
+        <v>42.48849572799745</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>18.65741634708677</v>
+        <v>40.36407094159757</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -5488,6 +5670,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.6393856285124</v>
+      </c>
+      <c r="X14" t="n">
+        <v>18.65741634708678</v>
       </c>
     </row>
     <row r="15">
@@ -5506,10 +5694,10 @@
         <v>135.9466221061217</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23.95295567177541</v>
+        <v>54.55710856350098</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>34.55812299703496</v>
+        <v>104.4582731714328</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>106.7715334550433</v>
@@ -5540,6 +5728,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>369.1094243865741</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.95295567177542</v>
+      </c>
+      <c r="X15" t="n">
+        <v>34.55812299703499</v>
       </c>
     </row>
     <row r="16">
@@ -5558,10 +5752,10 @@
         <v>198.8985325430228</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.63460681952383</v>
+        <v>74.37003372497924</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45.33149009162165</v>
+        <v>143.3882984931256</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>137.6301009435799</v>
@@ -5592,6 +5786,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>501.5558102103201</v>
+      </c>
+      <c r="W16" t="n">
+        <v>30.63460681952385</v>
+      </c>
+      <c r="X16" t="n">
+        <v>45.33149009162168</v>
       </c>
     </row>
     <row r="17">
@@ -5610,10 +5810,10 @@
         <v>212.3501790805574</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>31.95864361544764</v>
+        <v>78.43981692551702</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>47.11052409775762</v>
+        <v>150.1985853488636</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>190.4213985989605</v>
@@ -5644,6 +5844,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>714.5229959820447</v>
+      </c>
+      <c r="W17" t="n">
+        <v>31.95864361544766</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47.11052409775765</v>
       </c>
     </row>
     <row r="18">
@@ -5662,10 +5868,10 @@
         <v>274.2438152264721</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.70607999636413</v>
+        <v>96.59934694520636</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>51.42650027905293</v>
+        <v>166.6386900205549</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>215.9447962327247</v>
@@ -5696,6 +5902,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>799.6778774752461</v>
+      </c>
+      <c r="W18" t="n">
+        <v>37.70607999636415</v>
+      </c>
+      <c r="X18" t="n">
+        <v>51.42650027905297</v>
       </c>
     </row>
     <row r="19">
@@ -5714,10 +5926,10 @@
         <v>197.4096693321098</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>30.48614216210158</v>
+        <v>73.91648819254831</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45.74791770852035</v>
+        <v>154.823544890068</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>115.6905971756402</v>
@@ -5748,6 +5960,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>403.9677184100817</v>
+      </c>
+      <c r="W19" t="n">
+        <v>30.48614216210159</v>
+      </c>
+      <c r="X19" t="n">
+        <v>45.74791770852038</v>
       </c>
     </row>
     <row r="20">
@@ -5766,10 +5984,10 @@
         <v>207.1083634605113</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.44632442053419</v>
+        <v>76.8597792817263</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45.75368795389788</v>
+        <v>153.2760119783852</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>121.7728402505769</v>
@@ -5800,6 +6018,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>407.0590343241895</v>
+      </c>
+      <c r="W20" t="n">
+        <v>31.44632442053421</v>
+      </c>
+      <c r="X20" t="n">
+        <v>45.75368795389792</v>
       </c>
     </row>
     <row r="21">
@@ -5818,10 +6042,10 @@
         <v>301.4101650091263</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40.08059115263882</v>
+        <v>104.3207961645008</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>53.01838556813867</v>
+        <v>168.74850520404</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>90.39104354497364</v>
@@ -5852,6 +6076,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>220.3508395022479</v>
+      </c>
+      <c r="W21" t="n">
+        <v>40.08059115263884</v>
+      </c>
+      <c r="X21" t="n">
+        <v>53.01838556813871</v>
       </c>
     </row>
     <row r="22">
@@ -5870,10 +6100,10 @@
         <v>519.3410259854718</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>56.97886270755139</v>
+        <v>162.4601570068622</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>92.62658375531083</v>
+        <v>367.0454442669831</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>194.5447660486892</v>
@@ -5904,6 +6134,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>507.8730374775016</v>
+      </c>
+      <c r="W22" t="n">
+        <v>56.97886270755142</v>
+      </c>
+      <c r="X22" t="n">
+        <v>92.6265837553109</v>
       </c>
     </row>
     <row r="23">
@@ -5922,10 +6158,10 @@
         <v>487.433966566042</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>54.69019188607412</v>
+        <v>154.2865766833415</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>74.92013991720984</v>
+        <v>266.7314096695782</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>121.806086684055</v>
@@ -5956,6 +6192,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>226.7381624294625</v>
+      </c>
+      <c r="W23" t="n">
+        <v>54.6901918860742</v>
+      </c>
+      <c r="X23" t="n">
+        <v>74.92013991720991</v>
       </c>
     </row>
     <row r="24">
@@ -5974,10 +6216,10 @@
         <v>487.433966566042</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>54.69019188607412</v>
+        <v>154.2865766833413</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>74.92013991720984</v>
+        <v>266.7314096695782</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>121.806086684055</v>
@@ -6008,6 +6250,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>219.6002639928552</v>
+      </c>
+      <c r="W24" t="n">
+        <v>54.69019188607416</v>
+      </c>
+      <c r="X24" t="n">
+        <v>74.92013991720991</v>
       </c>
     </row>
     <row r="25">
@@ -6026,10 +6274,10 @@
         <v>729.4475876486517</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>70.97554990353915</v>
+        <v>214.2227725429684</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>108.5928185469568</v>
+        <v>444.2904462808075</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>234.1706657610695</v>
@@ -6060,6 +6308,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>601.0195585056825</v>
+      </c>
+      <c r="W25" t="n">
+        <v>70.9755499035392</v>
+      </c>
+      <c r="X25" t="n">
+        <v>108.5928185469569</v>
       </c>
     </row>
     <row r="26">
@@ -6078,10 +6332,10 @@
         <v>213.9547080244107</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>32.11456885585057</v>
+        <v>78.92201350086717</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>52.46755458188604</v>
+        <v>192.983471774201</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>158.0915036153427</v>
@@ -6112,6 +6366,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>535.0091730086642</v>
+      </c>
+      <c r="W26" t="n">
+        <v>32.11456885585059</v>
+      </c>
+      <c r="X26" t="n">
+        <v>52.46755458188609</v>
       </c>
     </row>
     <row r="27">
@@ -6130,10 +6390,10 @@
         <v>1217.891849222865</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>98.86517997923724</v>
+        <v>325.1652671123289</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>153.0011451840076</v>
+        <v>703.9308239648649</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>327.6934916299169</v>
@@ -6164,6 +6424,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>791.5983927627544</v>
+      </c>
+      <c r="W27" t="n">
+        <v>98.86517997923731</v>
+      </c>
+      <c r="X27" t="n">
+        <v>153.0011451840078</v>
       </c>
     </row>
     <row r="28">
@@ -6182,10 +6448,10 @@
         <v>729.6653964256495</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>70.98925173501803</v>
+        <v>214.2748478281632</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>131.6867271529008</v>
+        <v>601.5216129553164</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>458.2915153155639</v>
@@ -6216,6 +6482,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>1584.88760675104</v>
+      </c>
+      <c r="W28" t="n">
+        <v>70.98925173501809</v>
+      </c>
+      <c r="X28" t="n">
+        <v>131.6867271529009</v>
       </c>
     </row>
     <row r="29">
@@ -6234,10 +6506,10 @@
         <v>629.8141419989535</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>64.54607353595769</v>
+        <v>190.0809925592281</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>110.6163159950011</v>
+        <v>480.6329562362836</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>315.0976886468638</v>
@@ -6268,6 +6540,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>962.9311990402859</v>
+      </c>
+      <c r="W29" t="n">
+        <v>64.54607353595777</v>
+      </c>
+      <c r="X29" t="n">
+        <v>110.6163159950012</v>
       </c>
     </row>
     <row r="30">
@@ -6286,10 +6564,10 @@
         <v>2211.896778349087</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>145.4133813846599</v>
+        <v>528.5576988200993</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>289.661472765462</v>
+        <v>1694.662426613107</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>829.1658323053221</v>
@@ -6321,6 +6599,12 @@
       <c r="V30" s="2" t="n">
         <v>2393.658992550364</v>
       </c>
+      <c r="W30" t="n">
+        <v>145.41338138466</v>
+      </c>
+      <c r="X30" t="n">
+        <v>289.6614727654623</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -6338,10 +6622,10 @@
         <v>6838.753212140276</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>301.6878562023358</v>
+        <v>1324.925758547592</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>487.3710733600373</v>
+        <v>3051.529362519855</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -6369,6 +6653,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>301.687856202336</v>
+      </c>
+      <c r="X31" t="n">
+        <v>487.3710733600379</v>
       </c>
     </row>
   </sheetData>
@@ -6382,7 +6672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6520,6 +6810,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6572,6 +6872,12 @@
       <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -6624,6 +6930,12 @@
       <c r="V3" s="2" t="n">
         <v>0.6891383286453481</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6676,6 +6988,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -6693,10 +7011,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.431634645197231</v>
+        <v>6.518320008100051</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.21005291293737</v>
+        <v>6.192404007695049</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.855217723189344</v>
@@ -6727,6 +7045,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>8.377866016624989</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.431634645197233</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.210052912937371</v>
       </c>
     </row>
     <row r="6">
@@ -6745,10 +7069,10 @@
         <v>15.84893192461114</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.968658602597495</v>
+        <v>9.483372579397724</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.276790985575142</v>
+        <v>13.28747019479956</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8.760193531723861</v>
@@ -6779,6 +7103,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>11.15628899878889</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.968658602597497</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7.276790985575144</v>
       </c>
     </row>
     <row r="7">
@@ -6797,10 +7127,10 @@
         <v>24.93687941796677</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8.001064059813308</v>
+        <v>13.71573211049736</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14.97556970612542</v>
+        <v>39.54220137686472</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>39.34555692831442</v>
@@ -6831,6 +7161,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>134.2340825475453</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.001064059813311</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14.97556970612543</v>
       </c>
     </row>
     <row r="8">
@@ -6849,10 +7185,10 @@
         <v>30.49372829387258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.112489038063083</v>
+        <v>16.15655423361635</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11.29118781331001</v>
+        <v>23.73538752207881</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40.2952399907787</v>
@@ -6883,6 +7219,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>150.5385962411484</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9.112489038063087</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.29118781331002</v>
       </c>
     </row>
     <row r="9">
@@ -6901,10 +7243,10 @@
         <v>41.78810060294223</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.17156947859833</v>
+        <v>20.88126393867481</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>19.38977618409366</v>
+        <v>52.02889058574307</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>48.21537006668882</v>
@@ -6935,6 +7277,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>163.4108729841161</v>
+      </c>
+      <c r="W9" t="n">
+        <v>11.17156947859834</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.38977618409368</v>
       </c>
     </row>
     <row r="10">
@@ -6953,10 +7301,10 @@
         <v>55.22112665807593</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.37773098302224</v>
+        <v>26.20052834456147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27.23502687204532</v>
+        <v>80.61658569663733</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>96.28327532558015</v>
@@ -6987,6 +7335,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>354.4675887538862</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13.37773098302224</v>
+      </c>
+      <c r="X10" t="n">
+        <v>27.23502687204535</v>
       </c>
     </row>
     <row r="11">
@@ -7005,10 +7359,10 @@
         <v>55.6241205887029</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.44077277831944</v>
+        <v>26.35609133602047</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>22.38140449187295</v>
+        <v>61.13100470127168</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>58.6373656133773</v>
@@ -7039,6 +7393,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>200.1370740273283</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13.44077277831945</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22.38140449187296</v>
       </c>
     </row>
     <row r="12">
@@ -7057,10 +7417,10 @@
         <v>79.43282347242813</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.92277198657578</v>
+        <v>35.22555040278327</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17.23483817689782</v>
+        <v>36.97949584824783</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>22.60924610892804</v>
@@ -7091,6 +7451,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>32.39206479916432</v>
+      </c>
+      <c r="W12" t="n">
+        <v>16.9227719865758</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.23483817689783</v>
       </c>
     </row>
     <row r="13">
@@ -7109,10 +7475,10 @@
         <v>79.43282347242813</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16.92277198657578</v>
+        <v>35.22555040278324</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>17.23483817689782</v>
+        <v>36.97949584824783</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>22.60924610892804</v>
@@ -7143,6 +7509,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>32.24210052753474</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.92277198657579</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.23483817689783</v>
       </c>
     </row>
     <row r="14">
@@ -7161,10 +7533,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.6393856285124</v>
+        <v>42.48849572799745</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>18.65741634708677</v>
+        <v>40.36407094159757</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -7195,6 +7567,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.6393856285124</v>
+      </c>
+      <c r="X14" t="n">
+        <v>18.65741634708678</v>
       </c>
     </row>
     <row r="15">
@@ -7213,10 +7591,10 @@
         <v>135.9466221061217</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23.95295567177541</v>
+        <v>54.55710856350098</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>34.55812299703496</v>
+        <v>104.4582731714328</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>106.7715334550433</v>
@@ -7247,6 +7625,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>369.1094243865741</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.95295567177542</v>
+      </c>
+      <c r="X15" t="n">
+        <v>34.55812299703499</v>
       </c>
     </row>
     <row r="16">
@@ -7265,10 +7649,10 @@
         <v>198.8985325430228</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.63460681952383</v>
+        <v>74.37003372497924</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45.33149009162165</v>
+        <v>143.3882984931256</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>137.6301009435799</v>
@@ -7299,6 +7683,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>501.5558102103201</v>
+      </c>
+      <c r="W16" t="n">
+        <v>30.63460681952385</v>
+      </c>
+      <c r="X16" t="n">
+        <v>45.33149009162168</v>
       </c>
     </row>
     <row r="17">
@@ -7317,10 +7707,10 @@
         <v>212.3501790805574</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>31.95864361544764</v>
+        <v>78.43981692551702</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>47.11052409775762</v>
+        <v>150.1985853488636</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>190.4213985989605</v>
@@ -7351,6 +7741,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>714.5229959820447</v>
+      </c>
+      <c r="W17" t="n">
+        <v>31.95864361544766</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47.11052409775765</v>
       </c>
     </row>
     <row r="18">
@@ -7369,10 +7765,10 @@
         <v>274.2438152264721</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.70607999636413</v>
+        <v>96.59934694520636</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>51.42650027905293</v>
+        <v>166.6386900205549</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>215.9447962327247</v>
@@ -7403,6 +7799,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>799.6778774752461</v>
+      </c>
+      <c r="W18" t="n">
+        <v>37.70607999636415</v>
+      </c>
+      <c r="X18" t="n">
+        <v>51.42650027905297</v>
       </c>
     </row>
     <row r="19">
@@ -7421,10 +7823,10 @@
         <v>197.4096693321098</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>30.48614216210158</v>
+        <v>73.91648819254831</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45.74791770852035</v>
+        <v>154.823544890068</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>115.6905971756402</v>
@@ -7455,6 +7857,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>403.9677184100817</v>
+      </c>
+      <c r="W19" t="n">
+        <v>30.48614216210159</v>
+      </c>
+      <c r="X19" t="n">
+        <v>45.74791770852038</v>
       </c>
     </row>
     <row r="20">
@@ -7473,10 +7881,10 @@
         <v>207.1083634605113</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.44632442053419</v>
+        <v>76.8597792817263</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45.75368795389788</v>
+        <v>153.2760119783852</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>121.7728402505769</v>
@@ -7507,6 +7915,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>407.0590343241895</v>
+      </c>
+      <c r="W20" t="n">
+        <v>31.44632442053421</v>
+      </c>
+      <c r="X20" t="n">
+        <v>45.75368795389792</v>
       </c>
     </row>
     <row r="21">
@@ -7525,10 +7939,10 @@
         <v>301.4101650091263</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40.08059115263882</v>
+        <v>104.3207961645008</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>53.01838556813867</v>
+        <v>168.74850520404</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>90.39104354497364</v>
@@ -7559,6 +7973,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>220.3508395022479</v>
+      </c>
+      <c r="W21" t="n">
+        <v>40.08059115263884</v>
+      </c>
+      <c r="X21" t="n">
+        <v>53.01838556813871</v>
       </c>
     </row>
     <row r="22">
@@ -7577,10 +7997,10 @@
         <v>519.3410259854718</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>56.97886270755139</v>
+        <v>162.4601570068622</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>92.62658375531083</v>
+        <v>367.0454442669831</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>194.5447660486892</v>
@@ -7611,6 +8031,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>507.8730374775016</v>
+      </c>
+      <c r="W22" t="n">
+        <v>56.97886270755142</v>
+      </c>
+      <c r="X22" t="n">
+        <v>92.6265837553109</v>
       </c>
     </row>
     <row r="23">
@@ -7629,10 +8055,10 @@
         <v>487.433966566042</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>54.69019188607412</v>
+        <v>154.2865766833415</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>74.92013991720984</v>
+        <v>266.7314096695782</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>121.806086684055</v>
@@ -7663,6 +8089,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>226.7381624294625</v>
+      </c>
+      <c r="W23" t="n">
+        <v>54.6901918860742</v>
+      </c>
+      <c r="X23" t="n">
+        <v>74.92013991720991</v>
       </c>
     </row>
     <row r="24">
@@ -7681,10 +8113,10 @@
         <v>487.433966566042</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>54.69019188607412</v>
+        <v>154.2865766833413</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>74.92013991720984</v>
+        <v>266.7314096695782</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>121.806086684055</v>
@@ -7715,6 +8147,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>219.6002639928552</v>
+      </c>
+      <c r="W24" t="n">
+        <v>54.69019188607416</v>
+      </c>
+      <c r="X24" t="n">
+        <v>74.92013991720991</v>
       </c>
     </row>
     <row r="25">
@@ -7733,10 +8171,10 @@
         <v>729.4475876486517</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>70.97554990353915</v>
+        <v>214.2227725429684</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>108.5928185469568</v>
+        <v>444.2904462808075</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>234.1706657610695</v>
@@ -7767,6 +8205,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>601.0195585056825</v>
+      </c>
+      <c r="W25" t="n">
+        <v>70.9755499035392</v>
+      </c>
+      <c r="X25" t="n">
+        <v>108.5928185469569</v>
       </c>
     </row>
     <row r="26">
@@ -7785,10 +8229,10 @@
         <v>213.9547080244107</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>32.11456885585057</v>
+        <v>78.92201350086717</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>52.46755458188604</v>
+        <v>192.983471774201</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>158.0915036153427</v>
@@ -7819,6 +8263,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>535.0091730086642</v>
+      </c>
+      <c r="W26" t="n">
+        <v>32.11456885585059</v>
+      </c>
+      <c r="X26" t="n">
+        <v>52.46755458188609</v>
       </c>
     </row>
     <row r="27">
@@ -7837,10 +8287,10 @@
         <v>1217.891849222865</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>98.86517997923724</v>
+        <v>325.1652671123289</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>153.0011451840076</v>
+        <v>703.9308239648649</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>327.6934916299169</v>
@@ -7871,6 +8321,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>791.5983927627544</v>
+      </c>
+      <c r="W27" t="n">
+        <v>98.86517997923731</v>
+      </c>
+      <c r="X27" t="n">
+        <v>153.0011451840078</v>
       </c>
     </row>
     <row r="28">
@@ -7889,10 +8345,10 @@
         <v>729.6653964256495</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>70.98925173501803</v>
+        <v>214.2748478281632</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>131.6867271529008</v>
+        <v>601.5216129553164</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>458.2915153155639</v>
@@ -7923,6 +8379,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>1584.88760675104</v>
+      </c>
+      <c r="W28" t="n">
+        <v>70.98925173501809</v>
+      </c>
+      <c r="X28" t="n">
+        <v>131.6867271529009</v>
       </c>
     </row>
     <row r="29">
@@ -7941,10 +8403,10 @@
         <v>629.8141419989535</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>64.54607353595769</v>
+        <v>190.0809925592281</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>110.6163159950011</v>
+        <v>480.6329562362836</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>315.0976886468638</v>
@@ -7975,6 +8437,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>962.9311990402859</v>
+      </c>
+      <c r="W29" t="n">
+        <v>64.54607353595777</v>
+      </c>
+      <c r="X29" t="n">
+        <v>110.6163159950012</v>
       </c>
     </row>
     <row r="30">
@@ -7993,10 +8461,10 @@
         <v>2211.896778349087</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>145.4133813846599</v>
+        <v>528.5576988200993</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>289.661472765462</v>
+        <v>1694.662426613107</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>829.1658323053221</v>
@@ -8028,6 +8496,12 @@
       <c r="V30" s="2" t="n">
         <v>2393.658992550364</v>
       </c>
+      <c r="W30" t="n">
+        <v>145.41338138466</v>
+      </c>
+      <c r="X30" t="n">
+        <v>289.6614727654623</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -8045,10 +8519,10 @@
         <v>6838.753212140276</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>301.6878562023358</v>
+        <v>1324.925758547592</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>487.3710733600373</v>
+        <v>3051.529362519855</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -8079,6 +8553,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>301.687856202336</v>
+      </c>
+      <c r="X31" t="n">
+        <v>487.3710733600379</v>
       </c>
     </row>
   </sheetData>
@@ -9029,7 +9509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9123,16 +9603,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>272.6487018382484</v>
+        <v>661.7961753055361</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>272.6487018382484</v>
+        <v>661.7961753055361</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.07469827447623242</v>
+        <v>0.1813140206316537</v>
       </c>
     </row>
     <row r="5">
@@ -9142,22 +9622,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>405.0600125917821</v>
+        <v>1345.340157481187</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>405.0600125917821</v>
+        <v>1345.340157481187</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>324.5865850649393</v>
+        <v>1113.72765515702</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>3650</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1109753459155567</v>
+        <v>0.3685863445153936</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0889278315246409</v>
+        <v>0.3051308644265808</v>
       </c>
     </row>
     <row r="6">
@@ -9450,6 +9930,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.7903750421689635</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>272.6487018382485</v>
+      </c>
+      <c r="C22" t="n">
+        <v>272.6487018382485</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.07469827447623248</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>405.0600125917824</v>
+      </c>
+      <c r="C23" t="n">
+        <v>405.0600125917824</v>
+      </c>
+      <c r="D23" t="n">
+        <v>324.5865850649396</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1109753459155568</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.08892783152464098</v>
       </c>
     </row>
   </sheetData>
@@ -9585,7 +10109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9760,7 +10284,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9777,7 +10301,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10053,6 +10577,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
